--- a/3_Component_Results/PRIVCON/Tables/naive_tbl/AVERAGE_10_9_qoq_forecast_error_table_first_eval.xlsx
+++ b/3_Component_Results/PRIVCON/Tables/naive_tbl/AVERAGE_10_9_qoq_forecast_error_table_first_eval.xlsx
@@ -447,22 +447,22 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>0.1560082246840916</v>
+        <v>0.160208903609589</v>
       </c>
       <c r="C2">
-        <v>1.334666554170477</v>
+        <v>1.316200726759697</v>
       </c>
       <c r="D2">
-        <v>7.673042805661654</v>
+        <v>7.528180597019461</v>
       </c>
       <c r="E2">
-        <v>2.770025777075306</v>
+        <v>2.743753013122621</v>
       </c>
       <c r="F2">
-        <v>2.793148460838132</v>
+        <v>2.765794969998897</v>
       </c>
       <c r="G2">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -470,22 +470,22 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>0.07663322156689945</v>
+        <v>0.07887358849788428</v>
       </c>
       <c r="C3">
-        <v>1.299834471760893</v>
+        <v>1.27809050045278</v>
       </c>
       <c r="D3">
-        <v>7.386217108190144</v>
+        <v>7.242103826281829</v>
       </c>
       <c r="E3">
-        <v>2.7177595751262</v>
+        <v>2.691115721458635</v>
       </c>
       <c r="F3">
-        <v>2.744260142950399</v>
+        <v>2.716726051515994</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -493,22 +493,22 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>0.1568606132576995</v>
+        <v>0.1587646097645884</v>
       </c>
       <c r="C4">
-        <v>1.29112821977527</v>
+        <v>1.270346864151808</v>
       </c>
       <c r="D4">
-        <v>7.117402227092668</v>
+        <v>6.97632487184498</v>
       </c>
       <c r="E4">
-        <v>2.667845990137487</v>
+        <v>2.641273342886908</v>
       </c>
       <c r="F4">
-        <v>2.690829533573063</v>
+        <v>2.663264582281677</v>
       </c>
       <c r="G4">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -516,22 +516,22 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>0.0935746678326199</v>
+        <v>0.09612204148316228</v>
       </c>
       <c r="C5">
-        <v>1.365793217520896</v>
+        <v>1.342376947300249</v>
       </c>
       <c r="D5">
-        <v>7.57656095386177</v>
+        <v>7.422910665061382</v>
       </c>
       <c r="E5">
-        <v>2.752555349827097</v>
+        <v>2.724501911370477</v>
       </c>
       <c r="F5">
-        <v>2.78007587260341</v>
+        <v>2.751022119488508</v>
       </c>
       <c r="G5">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -539,22 +539,22 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>0.1424348649439729</v>
+        <v>0.1473109550086592</v>
       </c>
       <c r="C6">
-        <v>1.381738402566604</v>
+        <v>1.360795668930818</v>
       </c>
       <c r="D6">
-        <v>8.024261160333362</v>
+        <v>7.860042023717354</v>
       </c>
       <c r="E6">
-        <v>2.832712685807257</v>
+        <v>2.803576648447007</v>
       </c>
       <c r="F6">
-        <v>2.859715526557411</v>
+        <v>2.829331145304322</v>
       </c>
       <c r="G6">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -562,22 +562,22 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>0.1732741012286916</v>
+        <v>0.1737969200002274</v>
       </c>
       <c r="C7">
-        <v>1.574991177320644</v>
+        <v>1.539572532602642</v>
       </c>
       <c r="D7">
-        <v>9.359491832855587</v>
+        <v>9.120466548879834</v>
       </c>
       <c r="E7">
-        <v>3.05932865721478</v>
+        <v>3.020011018006364</v>
       </c>
       <c r="F7">
-        <v>3.095418501638419</v>
+        <v>3.054419515871751</v>
       </c>
       <c r="G7">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -585,22 +585,22 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>0.2044873955334486</v>
+        <v>0.2213269651968121</v>
       </c>
       <c r="C8">
-        <v>1.562635388531142</v>
+        <v>1.543734221536671</v>
       </c>
       <c r="D8">
-        <v>9.505286999794503</v>
+        <v>9.273910926985746</v>
       </c>
       <c r="E8">
-        <v>3.083064546809636</v>
+        <v>3.045309660278531</v>
       </c>
       <c r="F8">
-        <v>3.118709047737856</v>
+        <v>3.078026576705836</v>
       </c>
       <c r="G8">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -608,22 +608,22 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>-0.09975482970692948</v>
+        <v>-0.03934568386280961</v>
       </c>
       <c r="C9">
-        <v>2.241897685767165</v>
+        <v>2.190799568969661</v>
       </c>
       <c r="D9">
-        <v>15.38488210364042</v>
+        <v>14.71732488333816</v>
       </c>
       <c r="E9">
-        <v>3.922356702754152</v>
+        <v>3.836316577569968</v>
       </c>
       <c r="F9">
-        <v>4.022951401199263</v>
+        <v>3.93084795438904</v>
       </c>
       <c r="G9">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -631,22 +631,22 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>-0.8689250956944341</v>
+        <v>-0.7575688501960079</v>
       </c>
       <c r="C10">
-        <v>2.089385287080378</v>
+        <v>1.989433648094889</v>
       </c>
       <c r="D10">
-        <v>12.84994429113759</v>
+        <v>11.96610441568903</v>
       </c>
       <c r="E10">
-        <v>3.584681895390105</v>
+        <v>3.459205749256472</v>
       </c>
       <c r="F10">
-        <v>3.619782165404088</v>
+        <v>3.502644209304035</v>
       </c>
       <c r="G10">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:7">
